--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D35DD9F-5813-4D1E-AAA0-26DD20FF084D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D45808-21CE-4C12-AE6B-77AB36602E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="194">
   <si>
     <t>type</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>resultado_tdr</t>
+  </si>
+  <si>
+    <t>cs</t>
   </si>
 </sst>
 </file>
@@ -3244,6 +3247,14 @@
         <v>107</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>98</v>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D45808-21CE-4C12-AE6B-77AB36602E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A9E202-0384-4B6A-A208-56CBDB9769F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="196">
   <si>
     <t>type</t>
   </si>
@@ -636,6 +636,12 @@
   </si>
   <si>
     <t>cs</t>
+  </si>
+  <si>
+    <t>id_formssentinela</t>
+  </si>
+  <si>
+    <t>comentario_1</t>
   </si>
 </sst>
 </file>
@@ -767,7 +773,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -786,12 +792,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -815,7 +815,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1318,9 +1317,9 @@
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="8" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="15.75" style="7" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.125" style="2" customWidth="1"/>
     <col min="9" max="9" width="29.75" style="2" customWidth="1"/>
@@ -1343,19 +1342,19 @@
       <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I1" t="s">
@@ -1376,10 +1375,10 @@
       <c r="N1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="16" t="s">
         <v>91</v>
       </c>
       <c r="Q1" t="s">
@@ -1413,7 +1412,7 @@
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="10"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1423,7 +1422,7 @@
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="10"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1435,15 +1434,15 @@
       <c r="B4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="C4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>184</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1452,7 +1451,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6"/>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -1465,27 +1464,27 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C8" s="9"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
+      <c r="C8" s="7"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C9" s="9"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="10"/>
+      <c r="C9" s="7"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="9"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="2"/>
       <c r="F10" s="2"/>
       <c r="H10"/>
       <c r="I10"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1493,359 +1492,359 @@
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C17" s="10"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="10"/>
+      <c r="C17" s="8"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="9"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="C18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="9"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="10"/>
+      <c r="C19" s="7"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="9"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="10"/>
+      <c r="C20" s="7"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="9"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="10"/>
+      <c r="C21" s="7"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="9"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="10"/>
+      <c r="C22" s="7"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="9"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="10"/>
+      <c r="C23" s="7"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="8"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="9"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="10"/>
+      <c r="C24" s="7"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C25" s="10"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="10"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="8"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="9"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
+      <c r="C26" s="7"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="9"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
+      <c r="C27" s="7"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
       <c r="K29" s="4"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
       <c r="K30" s="4"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="11"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="11"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="9"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="10"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="10"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="10"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="10"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8"/>
     </row>
     <row r="49" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="10"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8"/>
     </row>
     <row r="50" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="10"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8"/>
     </row>
     <row r="51" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="10"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8"/>
     </row>
     <row r="52" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="10"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8"/>
     </row>
     <row r="53" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="10"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8"/>
     </row>
     <row r="54" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="10"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8"/>
     </row>
     <row r="55" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="10"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8"/>
     </row>
     <row r="56" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="10"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8"/>
     </row>
     <row r="57" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="10"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8"/>
     </row>
     <row r="58" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="10"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8"/>
     </row>
     <row r="59" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="10"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8"/>
     </row>
     <row r="60" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="10"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8"/>
     </row>
     <row r="61" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="10"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8"/>
     </row>
     <row r="62" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="10"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8"/>
     </row>
     <row r="63" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="10"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8"/>
     </row>
     <row r="64" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="10"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8"/>
     </row>
     <row r="65" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="10"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="8"/>
     </row>
     <row r="66" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="10"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="8"/>
     </row>
     <row r="67" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="10"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="8"/>
     </row>
     <row r="68" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="10"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="8"/>
     </row>
     <row r="69" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="10"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="8"/>
     </row>
     <row r="70" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="10"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="8"/>
     </row>
     <row r="71" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="10"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="8"/>
     </row>
     <row r="72" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="10"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="8"/>
     </row>
     <row r="73" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="10"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2129,7 +2128,7 @@
       <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -2140,7 +2139,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -2151,7 +2150,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -2162,7 +2161,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -2173,7 +2172,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -2184,7 +2183,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -2195,7 +2194,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -2206,7 +2205,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2217,7 +2216,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -2228,7 +2227,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2239,7 +2238,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2250,7 +2249,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2261,7 +2260,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -2272,7 +2271,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2283,7 +2282,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -2294,7 +2293,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -2305,7 +2304,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -2316,7 +2315,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -2327,7 +2326,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -2338,7 +2337,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -2349,7 +2348,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -2360,7 +2359,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -2371,7 +2370,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -2382,7 +2381,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -2393,7 +2392,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -2404,7 +2403,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -2415,7 +2414,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -2426,7 +2425,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -2437,7 +2436,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -2448,7 +2447,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -2852,38 +2851,38 @@
     <col min="11" max="11" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="19" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2952,12 +2951,12 @@
       <c r="G5" t="s">
         <v>183</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="18" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H6" s="21"/>
+      <c r="H6" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2976,17 +2975,17 @@
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="16" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3088,18 +3087,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3107,119 +3106,119 @@
       <c r="A3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="2" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3240,10 +3239,10 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="2" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3255,6 +3254,14 @@
         <v>193</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>194</v>
+      </c>
+    </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>98</v>
@@ -3279,21 +3286,33 @@
         <v>188</v>
       </c>
     </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="9"/>
+      <c r="A31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="9"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A9E202-0384-4B6A-A208-56CBDB9769F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4E8D8C-1B6C-47EC-8E9F-3CAB40259FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="198">
   <si>
     <t>type</t>
   </si>
@@ -643,12 +643,18 @@
   <si>
     <t>comentario_1</t>
   </si>
+  <si>
+    <t>select_one_dropdown</t>
+  </si>
+  <si>
+    <t>comentario</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -685,12 +691,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -773,7 +773,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -811,15 +811,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1354,7 +1351,7 @@
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>32</v>
       </c>
       <c r="I1" t="s">
@@ -1375,10 +1372,10 @@
       <c r="N1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="15" t="s">
         <v>91</v>
       </c>
       <c r="Q1" t="s">
@@ -1621,21 +1618,21 @@
       <c r="H35" s="9"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="20"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="19"/>
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="20"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="19"/>
       <c r="H37" s="9"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
@@ -2851,38 +2848,38 @@
     <col min="11" max="11" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="18" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2951,12 +2948,12 @@
       <c r="G5" t="s">
         <v>183</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H6" s="18"/>
+      <c r="H6" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2975,17 +2972,17 @@
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3079,7 +3076,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -3087,83 +3084,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3171,63 +3168,63 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3235,36 +3232,47 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" t="s">
-        <v>194</v>
+      <c r="B25" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>186</v>
@@ -3295,24 +3303,28 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="7"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4E8D8C-1B6C-47EC-8E9F-3CAB40259FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24E901F-1143-47C6-95C8-348166BCDE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="190">
   <si>
     <t>type</t>
   </si>
@@ -123,15 +123,6 @@
     <t>mes</t>
   </si>
   <si>
-    <t>region_csv</t>
-  </si>
-  <si>
-    <t>sector_csv</t>
-  </si>
-  <si>
-    <t>local_csv</t>
-  </si>
-  <si>
     <t>choice_filter</t>
   </si>
   <si>
@@ -162,26 +153,6 @@
     <t>hideInContents</t>
   </si>
   <si>
-    <t>csv</t>
-  </si>
-  <si>
-    <t>_.chain(context)
-.uniq(function(x){return x.sector;})
-.map(function(place){
-    return {
-        data_value:place.sector, 
-        region: place.region,
-        display:{title: {text: place.sector} }
-    } 
-    })
-.value()</t>
-  </si>
-  <si>
-    <t>_.chain(context).pluck('region').uniq().map(function(region){
-return {data_value:region, display:{title: {text: region} } };
-}).value()</t>
-  </si>
-  <si>
     <t>callback</t>
   </si>
   <si>
@@ -194,9 +165,6 @@
     <t>query_name</t>
   </si>
   <si>
-    <t>"tabancas.csv"</t>
-  </si>
-  <si>
     <t>Masculino</t>
   </si>
   <si>
@@ -288,18 +256,6 @@
   </si>
   <si>
     <t>[data('id_paciente')]</t>
-  </si>
-  <si>
-    <t>_.chain(context)
-.map(function(place){
-    return {
-        data_value:place.tabanca, 
-        region: place.region,
-        sector: place.sector,
-               display:{title: {text: place.tabanca} }
-    } 
-    })
-.value()</t>
   </si>
   <si>
     <t>Comentário</t>
@@ -1268,7 +1224,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1284,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1292,7 +1248,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1287,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
@@ -1352,7 +1308,7 @@
         <v>20</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
         <v>21</v>
@@ -1367,37 +1323,37 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" t="s">
         <v>33</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>35</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>36</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>37</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>38</v>
-      </c>
-      <c r="U1" t="s">
-        <v>39</v>
-      </c>
-      <c r="V1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W1" t="s">
-        <v>41</v>
       </c>
       <c r="X1" t="s">
         <v>19</v>
@@ -1429,7 +1385,7 @@
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C4" s="7"/>
       <c r="E4" s="8"/>
@@ -1437,27 +1393,27 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D5" s="8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="D6" s="8" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1482,10 +1438,10 @@
         <v>4</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1894,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1905,12 +1861,12 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1921,13 +1877,13 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1936,24 +1892,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1962,101 +1918,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2126,332 +2082,332 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2833,7 +2789,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C574FB-861C-4A83-BA50-230986D05032}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
@@ -2850,110 +2806,67 @@
   <sheetData>
     <row r="1" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="C2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="J2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G5" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H6" s="17"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2974,44 +2887,44 @@
   <sheetData>
     <row r="1" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3030,42 +2943,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3076,7 +2989,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -3093,10 +3006,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3104,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3112,12 +3025,12 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>26</v>
@@ -3144,12 +3057,12 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>23</v>
@@ -3157,10 +3070,10 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3176,23 +3089,23 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3200,31 +3113,31 @@
         <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3232,7 +3145,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3240,67 +3153,68 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
@@ -3321,10 +3235,6 @@
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24E901F-1143-47C6-95C8-348166BCDE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EFDD97-B57E-4281-A8CB-C24CFB6BE3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="191">
   <si>
     <t>type</t>
   </si>
@@ -255,9 +255,6 @@
     <t>id_paciente=?</t>
   </si>
   <si>
-    <t>[data('id_paciente')]</t>
-  </si>
-  <si>
     <t>Comentário</t>
   </si>
   <si>
@@ -561,9 +558,6 @@
     <t xml:space="preserve">resultado </t>
   </si>
   <si>
-    <t>{id_paciente: data('id_paciente'), nome: data('nome'), nome_casa: data('nome_casa'), sexo: data('sexo'), dn: data('dn'), ano: data('ano'), mes: data('mes'), af: data('af'), id_formssentinela: data('_id')}</t>
-  </si>
-  <si>
     <t>intro_resultado</t>
   </si>
   <si>
@@ -604,6 +598,15 @@
   </si>
   <si>
     <t>comentario</t>
+  </si>
+  <si>
+    <t>[opendatakit.getCurrentInstanceId()]</t>
+  </si>
+  <si>
+    <t>{id_formssentinela: opendatakit.getCurrentInstanceId(), id_paciente: data('id_paciente'), nome: data('nome'), nome_casa: data('nome_casa'), sexo: data('sexo'), dn: data('dn'), ano: data('ano'), mes: data('mes')}</t>
+  </si>
+  <si>
+    <t>numero_codigo</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1240,7 +1243,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1248,7 +1251,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1329,10 +1332,10 @@
         <v>31</v>
       </c>
       <c r="O1" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>83</v>
       </c>
       <c r="Q1" t="s">
         <v>32</v>
@@ -1396,10 +1399,10 @@
         <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1408,7 +1411,7 @@
         <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1438,10 +1441,10 @@
         <v>4</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1866,7 +1869,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1877,7 +1880,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1918,101 +1921,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2082,332 +2085,332 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2841,25 +2844,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>71</v>
@@ -2951,34 +2954,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
         <v>80</v>
-      </c>
-      <c r="B3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3006,10 +3009,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3017,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3025,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3054,7 +3057,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>51</v>
@@ -3089,15 +3092,15 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3105,7 +3108,7 @@
         <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3113,31 +3116,31 @@
         <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3145,7 +3148,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3153,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3161,7 +3164,15 @@
         <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>186</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3169,7 +3180,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3177,7 +3188,7 @@
         <v>10</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3185,23 +3196,23 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3209,7 +3220,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EFDD97-B57E-4281-A8CB-C24CFB6BE3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1F30CD-3689-4484-AF5C-D40B505D8FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="186">
   <si>
     <t>type</t>
   </si>
@@ -324,15 +324,9 @@
     <t>hospitaliza</t>
   </si>
   <si>
-    <t>tdr</t>
-  </si>
-  <si>
     <t>resultado</t>
   </si>
   <si>
-    <t>tdr_resultado</t>
-  </si>
-  <si>
     <t>Paludismo (malária)</t>
   </si>
   <si>
@@ -564,15 +558,6 @@
     <t>Introducão dos resultados de laboratorio</t>
   </si>
   <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>leuco</t>
-  </si>
-  <si>
-    <t>hb</t>
-  </si>
-  <si>
     <t>DOB_idade</t>
   </si>
   <si>
@@ -591,9 +576,6 @@
     <t>id_formssentinela</t>
   </si>
   <si>
-    <t>comentario_1</t>
-  </si>
-  <si>
     <t>select_one_dropdown</t>
   </si>
   <si>
@@ -607,6 +589,9 @@
   </si>
   <si>
     <t>numero_codigo</t>
+  </si>
+  <si>
+    <t>csname</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1228,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1399,10 +1384,10 @@
         <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1411,7 +1396,7 @@
         <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1869,7 +1854,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1880,7 +1865,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1921,101 +1906,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2088,10 +2073,10 @@
         <v>93</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2099,10 +2084,10 @@
         <v>93</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2110,10 +2095,10 @@
         <v>93</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2121,10 +2106,10 @@
         <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2132,10 +2117,10 @@
         <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2143,10 +2128,10 @@
         <v>93</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2154,10 +2139,10 @@
         <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2165,10 +2150,10 @@
         <v>93</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2176,10 +2161,10 @@
         <v>93</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2187,10 +2172,10 @@
         <v>93</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2198,10 +2183,10 @@
         <v>93</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2209,10 +2194,10 @@
         <v>93</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2220,10 +2205,10 @@
         <v>93</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2231,10 +2216,10 @@
         <v>93</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2242,10 +2227,10 @@
         <v>93</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2253,10 +2238,10 @@
         <v>93</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2264,10 +2249,10 @@
         <v>93</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2275,10 +2260,10 @@
         <v>93</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2286,10 +2271,10 @@
         <v>93</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2297,10 +2282,10 @@
         <v>93</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2308,10 +2293,10 @@
         <v>93</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2319,10 +2304,10 @@
         <v>93</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2330,10 +2315,10 @@
         <v>93</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2341,10 +2326,10 @@
         <v>93</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2352,10 +2337,10 @@
         <v>93</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2363,10 +2348,10 @@
         <v>93</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2374,10 +2359,10 @@
         <v>93</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2385,10 +2370,10 @@
         <v>93</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2396,10 +2381,10 @@
         <v>93</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2407,10 +2392,10 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2844,25 +2829,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>71</v>
@@ -2973,7 +2958,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -2992,7 +2977,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -3020,7 +3005,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3028,7 +3013,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3129,7 +3114,7 @@
     </row>
     <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>93</v>
@@ -3137,7 +3122,7 @@
     </row>
     <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>94</v>
@@ -3156,7 +3141,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3164,7 +3149,7 @@
         <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3172,80 +3157,40 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>98</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>178</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\sentinela\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1F30CD-3689-4484-AF5C-D40B505D8FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D54C2C-1A27-476F-865B-B415163325F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="187">
   <si>
     <t>type</t>
   </si>
@@ -592,6 +592,9 @@
   </si>
   <si>
     <t>csname</t>
+  </si>
+  <si>
+    <t>consultor</t>
   </si>
 </sst>
 </file>
@@ -3169,8 +3172,12 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D54C2C-1A27-476F-865B-B415163325F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF7D267-4A66-48EB-B5EF-AD17CDAE3790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2983,7 +2983,7 @@
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="32.375" customWidth="1"/>
     <col min="2" max="2" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3115,7 +3115,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>180</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>180</v>
       </c>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF7D267-4A66-48EB-B5EF-AD17CDAE3790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219A18D5-84C8-41C4-B96A-49900B116BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -2983,7 +2983,7 @@
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.375" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
     <col min="2" max="2" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3115,7 +3115,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>180</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>180</v>
       </c>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219A18D5-84C8-41C4-B96A-49900B116BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9EC6DE-4BAC-47F4-A559-1EF8FCDE77FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="189">
   <si>
     <t>type</t>
   </si>
@@ -595,6 +595,12 @@
   </si>
   <si>
     <t>consultor</t>
+  </si>
+  <si>
+    <t>esp_diagnostico</t>
+  </si>
+  <si>
+    <t>esp_diagnostico_secudario</t>
   </si>
 </sst>
 </file>
@@ -3180,12 +3186,20 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9EC6DE-4BAC-47F4-A559-1EF8FCDE77FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA237674-910D-4379-B82A-A2ED8F7DFFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="211">
   <si>
     <t>type</t>
   </si>
@@ -552,12 +552,6 @@
     <t xml:space="preserve">resultado </t>
   </si>
   <si>
-    <t>intro_resultado</t>
-  </si>
-  <si>
-    <t>Introducão dos resultados de laboratorio</t>
-  </si>
-  <si>
     <t>DOB_idade</t>
   </si>
   <si>
@@ -601,6 +595,78 @@
   </si>
   <si>
     <t>esp_diagnostico_secudario</t>
+  </si>
+  <si>
+    <t>nota_1</t>
+  </si>
+  <si>
+    <t>Centro: {{data.csname}} Data: {{calculates.hoje_display}}</t>
+  </si>
+  <si>
+    <t>Idade ou data de nascimento?</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='1'</t>
+  </si>
+  <si>
+    <t>else</t>
+  </si>
+  <si>
+    <t>Idades em anos</t>
+  </si>
+  <si>
+    <t>se for menos de 1 ano coloca zero</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='2'</t>
+  </si>
+  <si>
+    <t>data('ano')&lt;5</t>
+  </si>
+  <si>
+    <t>Idade em meses</t>
+  </si>
+  <si>
+    <t>se nao souber coloca zero, se for 12 acrescenta 1 ano</t>
+  </si>
+  <si>
+    <t>data('mes')&lt;12</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='2' &amp;&amp; data('ano')&lt;5</t>
+  </si>
+  <si>
+    <t>end if</t>
+  </si>
+  <si>
+    <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
+  </si>
+  <si>
+    <t>Nome e Apelido</t>
+  </si>
+  <si>
+    <t>Nome de Casa</t>
+  </si>
+  <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>data('sexo')=='2' &amp;&amp; (calculates.idade_mes()&lt;=660 &amp;&amp; calculates.idade_mes()&gt;=144)</t>
+  </si>
+  <si>
+    <t>calculates.letra_codigo() + data('numero_codigo')</t>
+  </si>
+  <si>
+    <t>Peso</t>
+  </si>
+  <si>
+    <t>data('peso')&lt;250</t>
+  </si>
+  <si>
+    <t>Proveniência (Bairro / Reigião)</t>
   </si>
 </sst>
 </file>
@@ -726,7 +792,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -770,6 +836,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1237,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1261,7 +1330,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y101"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1370,441 +1439,834 @@
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="3"/>
+      <c r="B3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3"/>
+      <c r="R3"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4"/>
-      <c r="B4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="D4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="2"/>
+      <c r="O4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="Y4" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="J5" s="19"/>
+      <c r="K5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6"/>
-      <c r="D6" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="F6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6"/>
+      <c r="R6"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+    </row>
+    <row r="12" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C8" s="7"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C9" s="7"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C10" s="7"/>
-      <c r="D10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="H10"/>
-      <c r="I10"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D14" s="8" t="s">
+      <c r="D16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O17" t="s">
+        <v>207</v>
+      </c>
+      <c r="P17" s="2"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="L19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+    </row>
+    <row r="22" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+    </row>
+    <row r="23" spans="1:18" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24"/>
+      <c r="R24"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" t="s">
+        <v>210</v>
+      </c>
+      <c r="L25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25"/>
+      <c r="R25"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28"/>
+      <c r="R28"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="19"/>
+      <c r="F29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O29" t="s">
+        <v>207</v>
+      </c>
+      <c r="P29" s="2"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30"/>
+      <c r="R30"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="C32" s="7"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C36" s="7"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="8"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C37" s="7"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C38" s="7"/>
+      <c r="D38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="H38"/>
+      <c r="I38"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D42" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F42" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="7"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="7"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="7"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="7"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="7"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="7"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C25" s="8"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="K29" s="4"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="K30" s="4"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C45" s="8"/>
+      <c r="E45" s="9"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C46" s="7"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C47" s="7"/>
+      <c r="E47" s="9"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C48" s="7"/>
+      <c r="E48" s="9"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C49" s="7"/>
+      <c r="E49" s="9"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C50" s="7"/>
+      <c r="E50" s="9"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C51" s="7"/>
+      <c r="E51" s="9"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C52" s="7"/>
+      <c r="E52" s="9"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C53" s="8"/>
+      <c r="E53" s="9"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C54" s="7"/>
+      <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C55" s="7"/>
+      <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8"/>
-    </row>
-    <row r="57" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="8"/>
-    </row>
-    <row r="58" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="8"/>
-    </row>
-    <row r="59" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="8"/>
-    </row>
-    <row r="60" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="61" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="8"/>
-    </row>
-    <row r="62" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="63" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="8"/>
-    </row>
-    <row r="65" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="8"/>
-    </row>
-    <row r="66" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="8"/>
-    </row>
-    <row r="67" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="8"/>
-    </row>
-    <row r="68" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="8"/>
-    </row>
-    <row r="69" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="8"/>
-    </row>
-    <row r="70" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="8"/>
-    </row>
-    <row r="71" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="8"/>
-    </row>
-    <row r="72" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="8"/>
-    </row>
-    <row r="73" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="9"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="9"/>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="8"/>
     </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="8"/>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="8"/>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="8"/>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="8"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="8"/>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="8"/>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="8"/>
+    </row>
+    <row r="81" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="8"/>
+    </row>
+    <row r="82" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="8"/>
+    </row>
+    <row r="83" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="8"/>
+    </row>
+    <row r="84" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="8"/>
+    </row>
+    <row r="85" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="8"/>
+    </row>
+    <row r="86" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="8"/>
+    </row>
+    <row r="87" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="8"/>
+    </row>
+    <row r="88" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="8"/>
+    </row>
+    <row r="89" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="8"/>
+    </row>
+    <row r="90" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="8"/>
+    </row>
+    <row r="91" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="8"/>
+    </row>
+    <row r="92" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="8"/>
+    </row>
+    <row r="93" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="8"/>
+    </row>
+    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="8"/>
+    </row>
+    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="8"/>
+    </row>
+    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="8"/>
+    </row>
+    <row r="97" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="8"/>
+    </row>
+    <row r="98" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="8"/>
+    </row>
+    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="8"/>
+    </row>
+    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="8"/>
+    </row>
+    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="8"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -1863,7 +2325,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1874,7 +2336,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1915,7 +2377,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
@@ -1926,7 +2388,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1937,7 +2399,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -1948,7 +2410,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
@@ -2853,10 +3315,10 @@
         <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>71</v>
@@ -2967,7 +3429,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -3014,7 +3476,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3022,7 +3484,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3123,7 +3585,7 @@
     </row>
     <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>93</v>
@@ -3131,7 +3593,7 @@
     </row>
     <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>94</v>
@@ -3150,7 +3612,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3158,7 +3620,7 @@
         <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3166,7 +3628,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3174,7 +3636,7 @@
         <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3182,7 +3644,7 @@
         <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3190,7 +3652,7 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3198,7 +3660,7 @@
         <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA237674-910D-4379-B82A-A2ED8F7DFFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EE5C9B-993E-4C23-B639-9CB6274C1D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1458,9 +1458,13 @@
       </c>
       <c r="J4" s="19"/>
       <c r="K4" s="2"/>
-      <c r="O4" s="2" t="s">
+      <c r="M4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" t="s">
         <v>77</v>
       </c>
+      <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4"/>
       <c r="R4"/>
@@ -1661,7 +1665,7 @@
       <c r="F17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="O17" t="s">
+      <c r="N17" t="s">
         <v>207</v>
       </c>
       <c r="P17" s="2"/>
@@ -1840,7 +1844,7 @@
       <c r="F29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="O29" t="s">
+      <c r="N29" t="s">
         <v>207</v>
       </c>
       <c r="P29" s="2"/>
@@ -1856,9 +1860,6 @@
       <c r="R30"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="D31" s="2"/>
       <c r="F31" s="2"/>
       <c r="O31" s="2"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EE5C9B-993E-4C23-B639-9CB6274C1D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EF21FC-4B66-4637-B9A3-665A343506DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="223">
   <si>
     <t>type</t>
   </si>
@@ -654,9 +654,6 @@
     <t>Sexo</t>
   </si>
   <si>
-    <t>data('sexo')=='2' &amp;&amp; (calculates.idade_mes()&lt;=660 &amp;&amp; calculates.idade_mes()&gt;=144)</t>
-  </si>
-  <si>
     <t>calculates.letra_codigo() + data('numero_codigo')</t>
   </si>
   <si>
@@ -667,6 +664,65 @@
   </si>
   <si>
     <t>Proveniência (Bairro / Reigião)</t>
+  </si>
+  <si>
+    <t>envio_tdr</t>
+  </si>
+  <si>
+    <t>O/A paciente foi enviada a fazer TDR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>inq</t>
+  </si>
+  <si>
+    <t>Inicias do Inqueridor</t>
+  </si>
+  <si>
+    <t>csv</t>
+  </si>
+  <si>
+    <t>"dx.csv"</t>
+  </si>
+  <si>
+    <t>dx_csv</t>
+  </si>
+  <si>
+    <t>sub_csv</t>
+  </si>
+  <si>
+    <t>_.chain(context)
+.uniq(function(x){return x.sub;})
+.map(function(place){
+    return {
+        data_value:place.sub, 
+        diagnostico: place.diagnostico,
+        display:{title: {text: place.sub} }
+    } 
+    })
+.value()</t>
+  </si>
+  <si>
+    <t>subdx_csv</t>
+  </si>
+  <si>
+    <t>_.chain(context).pluck('diagnostico').uniq().map(function(diagnostico){
+return {data_value:diagnostico, display:{title: {text: diagnostico_label} } };
+}).value()</t>
+  </si>
+  <si>
+    <t>_.chain(context)
+.map(function(place){
+    return {
+        data_value:place.subdx, 
+        diagnostico: place.diagnostico,
+        sub: place.sub,
+               display:{title: {text: place.subdx_label} }
+    } 
+    })
+.value()</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1322,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
@@ -1298,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2022010501</v>
+        <v>2022022800</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
@@ -1315,6 +1371,11 @@
       </c>
       <c r="B5" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -1658,16 +1719,10 @@
       <c r="R16"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D17" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="D17" s="2"/>
       <c r="E17" s="19"/>
-      <c r="F17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N17" t="s">
-        <v>207</v>
-      </c>
+      <c r="F17" s="2"/>
+      <c r="N17"/>
       <c r="P17" s="2"/>
       <c r="Q17"/>
       <c r="R17"/>
@@ -1755,13 +1810,7 @@
       <c r="Q22"/>
       <c r="R22"/>
     </row>
-    <row r="23" spans="1:18" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>206</v>
-      </c>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D23" s="2"/>
       <c r="F23" s="2"/>
       <c r="O23" s="2"/>
@@ -1777,10 +1826,10 @@
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -1796,7 +1845,7 @@
         <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L25" s="2" t="b">
         <v>1</v>
@@ -1815,9 +1864,6 @@
       <c r="R26"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="D27" s="2"/>
       <c r="F27" s="2"/>
       <c r="O27" s="2"/>
@@ -1845,7 +1891,7 @@
         <v>51</v>
       </c>
       <c r="N29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29"/>
@@ -1860,8 +1906,18 @@
       <c r="R30"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31"/>
@@ -1875,6 +1931,15 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34"/>
+      <c r="D34" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C36" s="7"/>
@@ -1882,9 +1947,15 @@
       <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C37" s="7"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="8"/>
+      <c r="D37" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C38" s="7"/>
@@ -1892,17 +1963,6 @@
       <c r="F38" s="2"/>
       <c r="H38"/>
       <c r="I38"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D42" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C45" s="8"/>
@@ -3249,7 +3309,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C574FB-861C-4A83-BA50-230986D05032}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.25" bestFit="1" customWidth="1"/>
@@ -3325,8 +3385,48 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H3" s="17"/>
+    <row r="3" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="J3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" t="s">
+        <v>216</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3669,12 +3769,20 @@
       <c r="B27" s="2"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+      <c r="A29" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>213</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EF21FC-4B66-4637-B9A3-665A343506DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2C8437-736A-49B9-9A27-C7971C487B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2C8437-736A-49B9-9A27-C7971C487B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3754F331-37E6-466B-8E81-0E7C6B7038E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="222">
   <si>
     <t>type</t>
   </si>
@@ -570,9 +570,6 @@
     <t>id_formssentinela</t>
   </si>
   <si>
-    <t>select_one_dropdown</t>
-  </si>
-  <si>
     <t>comentario</t>
   </si>
   <si>
@@ -681,48 +678,28 @@
     <t>Inicias do Inqueridor</t>
   </si>
   <si>
-    <t>csv</t>
-  </si>
-  <si>
-    <t>"dx.csv"</t>
-  </si>
-  <si>
-    <t>dx_csv</t>
-  </si>
-  <si>
-    <t>sub_csv</t>
-  </si>
-  <si>
-    <t>_.chain(context)
-.uniq(function(x){return x.sub;})
-.map(function(place){
-    return {
-        data_value:place.sub, 
-        diagnostico: place.diagnostico,
-        display:{title: {text: place.sub} }
-    } 
-    })
-.value()</t>
-  </si>
-  <si>
-    <t>subdx_csv</t>
-  </si>
-  <si>
-    <t>_.chain(context).pluck('diagnostico').uniq().map(function(diagnostico){
-return {data_value:diagnostico, display:{title: {text: diagnostico_label} } };
-}).value()</t>
-  </si>
-  <si>
-    <t>_.chain(context)
-.map(function(place){
-    return {
-        data_value:place.subdx, 
-        diagnostico: place.diagnostico,
-        sub: place.sub,
-               display:{title: {text: place.subdx_label} }
-    } 
-    })
-.value()</t>
+    <t>med</t>
+  </si>
+  <si>
+    <t>sub_dx</t>
+  </si>
+  <si>
+    <t>sub_dx2</t>
+  </si>
+  <si>
+    <t>saida</t>
+  </si>
+  <si>
+    <t>child_adult</t>
+  </si>
+  <si>
+    <t>calculates.idade_mes()&lt;216 ? "C" : "A"</t>
+  </si>
+  <si>
+    <t>letra_codigo</t>
+  </si>
+  <si>
+    <t>data('cs') + calculates.child_adult()</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1352,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -1540,10 +1517,10 @@
         <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="2"/>
@@ -1565,7 +1542,7 @@
         <v>172</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>1</v>
@@ -1577,10 +1554,10 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="D7" s="2"/>
       <c r="F7" s="2"/>
@@ -1600,7 +1577,7 @@
         <v>25</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1609,7 +1586,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D9" s="2"/>
       <c r="F9" s="2"/>
@@ -1626,13 +1603,13 @@
         <v>27</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -1641,10 +1618,10 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D11" s="2"/>
       <c r="F11" s="2"/>
@@ -1661,16 +1638,16 @@
         <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -1687,7 +1664,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D14" s="2"/>
       <c r="F14" s="2"/>
@@ -1698,7 +1675,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D15" s="2"/>
       <c r="F15" s="2"/>
@@ -1743,10 +1720,10 @@
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L19" s="2" t="b">
         <v>1</v>
@@ -1764,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L20" s="2" t="b">
         <v>1</v>
@@ -1782,7 +1759,7 @@
         <v>58</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1800,7 +1777,7 @@
         <v>24</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>1</v>
@@ -1826,10 +1803,10 @@
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -1845,7 +1822,7 @@
         <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L25" s="2" t="b">
         <v>1</v>
@@ -1891,7 +1868,7 @@
         <v>51</v>
       </c>
       <c r="N29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29"/>
@@ -1913,10 +1890,10 @@
         <v>46</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -1935,10 +1912,10 @@
         <v>56</v>
       </c>
       <c r="F34" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -3376,57 +3353,24 @@
         <v>72</v>
       </c>
       <c r="F2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G2" t="s">
         <v>180</v>
-      </c>
-      <c r="G2" t="s">
-        <v>181</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="63" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" t="s">
-        <v>215</v>
-      </c>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D3" s="2"/>
-      <c r="J3" t="s">
-        <v>216</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" t="s">
-        <v>215</v>
-      </c>
-      <c r="J4" t="s">
-        <v>216</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B5" t="s">
-        <v>215</v>
-      </c>
-      <c r="J5" t="s">
-        <v>216</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3494,7 +3438,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CAEF6-746F-4DFF-99B1-6DB036574858}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -3541,6 +3485,22 @@
         <v>84</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3549,7 +3509,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -3684,17 +3644,17 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>94</v>
@@ -3713,7 +3673,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3729,7 +3689,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3737,7 +3697,7 @@
         <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3745,7 +3705,7 @@
         <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3753,7 +3713,7 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3761,7 +3721,7 @@
         <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -3773,15 +3733,47 @@
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>213</v>
+      <c r="B29" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3754F331-37E6-466B-8E81-0E7C6B7038E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A8D5E4-7E65-4F37-8AC8-5D8882534A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="221">
   <si>
     <t>type</t>
   </si>
@@ -321,9 +321,6 @@
     <t>diagno_secund</t>
   </si>
   <si>
-    <t>hospitaliza</t>
-  </si>
-  <si>
     <t>resultado</t>
   </si>
   <si>
@@ -555,9 +552,6 @@
     <t>DOB_idade</t>
   </si>
   <si>
-    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : sc.getMonths(data('ano'), data('mes'))</t>
-  </si>
-  <si>
     <t>Criacão de Postos Sentinelas para seguimento do paludismo e outras doencas</t>
   </si>
   <si>
@@ -700,6 +694,9 @@
   </si>
   <si>
     <t>data('cs') + calculates.child_adult()</t>
+  </si>
+  <si>
+    <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10)</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1336,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1352,7 +1349,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -1517,10 +1514,10 @@
         <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J5" s="19"/>
       <c r="K5" s="2"/>
@@ -1536,13 +1533,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>1</v>
@@ -1554,10 +1551,10 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D7" s="2"/>
       <c r="F7" s="2"/>
@@ -1577,7 +1574,7 @@
         <v>25</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1586,7 +1583,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D9" s="2"/>
       <c r="F9" s="2"/>
@@ -1603,13 +1600,13 @@
         <v>27</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -1618,10 +1615,10 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D11" s="2"/>
       <c r="F11" s="2"/>
@@ -1638,16 +1635,16 @@
         <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -1664,7 +1661,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D14" s="2"/>
       <c r="F14" s="2"/>
@@ -1675,7 +1672,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D15" s="2"/>
       <c r="F15" s="2"/>
@@ -1720,10 +1717,10 @@
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L19" s="2" t="b">
         <v>1</v>
@@ -1741,7 +1738,7 @@
         <v>23</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="L20" s="2" t="b">
         <v>1</v>
@@ -1759,7 +1756,7 @@
         <v>58</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1777,7 +1774,7 @@
         <v>24</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>1</v>
@@ -1803,10 +1800,10 @@
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -1822,7 +1819,7 @@
         <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L25" s="2" t="b">
         <v>1</v>
@@ -1868,7 +1865,7 @@
         <v>51</v>
       </c>
       <c r="N29" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29"/>
@@ -1890,10 +1887,10 @@
         <v>46</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -1912,10 +1909,10 @@
         <v>56</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2363,7 +2360,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -2374,7 +2371,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2415,101 +2412,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2582,10 +2579,10 @@
         <v>93</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2593,10 +2590,10 @@
         <v>93</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2604,10 +2601,10 @@
         <v>93</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2615,10 +2612,10 @@
         <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2626,10 +2623,10 @@
         <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2637,10 +2634,10 @@
         <v>93</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2648,10 +2645,10 @@
         <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2659,10 +2656,10 @@
         <v>93</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2670,10 +2667,10 @@
         <v>93</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2681,10 +2678,10 @@
         <v>93</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2692,10 +2689,10 @@
         <v>93</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2703,10 +2700,10 @@
         <v>93</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2714,10 +2711,10 @@
         <v>93</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2725,10 +2722,10 @@
         <v>93</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2736,10 +2733,10 @@
         <v>93</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2747,10 +2744,10 @@
         <v>93</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2758,10 +2755,10 @@
         <v>93</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2769,10 +2766,10 @@
         <v>93</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2780,10 +2777,10 @@
         <v>93</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2791,10 +2788,10 @@
         <v>93</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2802,10 +2799,10 @@
         <v>93</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2813,10 +2810,10 @@
         <v>93</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2824,10 +2821,10 @@
         <v>93</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2835,10 +2832,10 @@
         <v>93</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2846,10 +2843,10 @@
         <v>93</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2857,10 +2854,10 @@
         <v>93</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2868,10 +2865,10 @@
         <v>93</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2879,10 +2876,10 @@
         <v>93</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2890,10 +2887,10 @@
         <v>93</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2901,10 +2898,10 @@
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3338,25 +3335,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>71</v>
@@ -3474,7 +3471,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -3487,18 +3484,18 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3537,7 +3534,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3545,7 +3542,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3661,19 +3658,15 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3681,7 +3674,7 @@
         <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3689,7 +3682,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3697,7 +3690,7 @@
         <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3705,7 +3698,7 @@
         <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3713,7 +3706,7 @@
         <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3721,7 +3714,7 @@
         <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -3733,7 +3726,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3741,7 +3734,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3749,7 +3742,7 @@
         <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3757,7 +3750,7 @@
         <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3765,7 +3758,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -3773,7 +3766,7 @@
         <v>10</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A8D5E4-7E65-4F37-8AC8-5D8882534A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C358BCC-6AAB-455C-9395-5FB434AA7DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="226">
   <si>
     <t>type</t>
   </si>
@@ -697,6 +697,21 @@
   </si>
   <si>
     <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10)</t>
+  </si>
+  <si>
+    <t>tto</t>
+  </si>
+  <si>
+    <t>quanti</t>
+  </si>
+  <si>
+    <t>unidade</t>
+  </si>
+  <si>
+    <t>freq</t>
+  </si>
+  <si>
+    <t>via</t>
   </si>
 </sst>
 </file>
@@ -3506,7 +3521,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -3769,6 +3784,46 @@
         <v>215</v>
       </c>
     </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C358BCC-6AAB-455C-9395-5FB434AA7DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75D6C3F-D104-462E-BB6C-8A1068D10C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="231">
   <si>
     <t>type</t>
   </si>
@@ -712,6 +712,21 @@
   </si>
   <si>
     <t>via</t>
+  </si>
+  <si>
+    <t>select_one_integer</t>
+  </si>
+  <si>
+    <t>(data('temperatura')&lt;46 &amp; data('temperatura')&gt;25) || !data('temperatura')</t>
+  </si>
+  <si>
+    <t>Temperatura</t>
+  </si>
+  <si>
+    <t>Febre</t>
+  </si>
+  <si>
+    <t>data('febre')== 1 | data('temperatura')&gt;38</t>
   </si>
 </sst>
 </file>
@@ -1380,13 +1395,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y101"/>
+  <dimension ref="A1:Y106"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="7" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
@@ -1545,7 +1560,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>171</v>
@@ -1707,7 +1722,7 @@
       <c r="Q16"/>
       <c r="R16"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D17" s="2"/>
       <c r="E17" s="19"/>
       <c r="F17" s="2"/>
@@ -1716,7 +1731,7 @@
       <c r="Q17"/>
       <c r="R17"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>49</v>
       </c>
@@ -1727,7 +1742,7 @@
       <c r="Q18"/>
       <c r="R18"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
         <v>5</v>
       </c>
@@ -1745,7 +1760,7 @@
       <c r="Q19"/>
       <c r="R19"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D20" s="2" t="s">
         <v>56</v>
       </c>
@@ -1763,7 +1778,7 @@
       <c r="Q20"/>
       <c r="R20"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
         <v>56</v>
       </c>
@@ -1778,9 +1793,9 @@
       <c r="Q21"/>
       <c r="R21"/>
     </row>
-    <row r="22" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>24</v>
@@ -1799,7 +1814,7 @@
       <c r="Q22"/>
       <c r="R22"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D23" s="2"/>
       <c r="F23" s="2"/>
       <c r="O23" s="2"/>
@@ -1807,7 +1822,7 @@
       <c r="Q23"/>
       <c r="R23"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
         <v>89</v>
       </c>
@@ -1825,7 +1840,7 @@
       <c r="Q24"/>
       <c r="R24"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
         <v>56</v>
       </c>
@@ -1844,7 +1859,7 @@
       <c r="Q25"/>
       <c r="R25"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D26" s="2"/>
       <c r="F26" s="2"/>
       <c r="O26" s="2"/>
@@ -1852,7 +1867,7 @@
       <c r="Q26"/>
       <c r="R26"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D27" s="2"/>
       <c r="F27" s="2"/>
       <c r="O27" s="2"/>
@@ -1860,7 +1875,7 @@
       <c r="Q27"/>
       <c r="R27"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>50</v>
       </c>
@@ -1871,7 +1886,7 @@
       <c r="Q28"/>
       <c r="R28"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
         <v>76</v>
       </c>
@@ -1886,106 +1901,151 @@
       <c r="Q29"/>
       <c r="R29"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D30" s="2"/>
-      <c r="F30" s="2"/>
+    <row r="30" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="D30" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J30" s="5"/>
+      <c r="K30" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
       <c r="Q30"/>
-      <c r="R30"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:18" ht="47.25" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="Q31"/>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+    </row>
+    <row r="33" spans="1:18" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D34" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G34" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31"/>
-      <c r="R31"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32"/>
-      <c r="C32" s="7"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-      <c r="D34" s="8" t="s">
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="C37" s="7"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="D39" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F39" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C36" s="7"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="8"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D37" s="8" t="s">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C41" s="7"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="8"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D42" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F42" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C38" s="7"/>
-      <c r="D38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="H38"/>
-      <c r="I38"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C45" s="8"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C46" s="7"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C47" s="7"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="8"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C48" s="7"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="7"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="8"/>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C43" s="7"/>
+      <c r="D43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="H43"/>
+      <c r="I43"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="7"/>
+      <c r="C50" s="8"/>
       <c r="E50" s="9"/>
       <c r="F50" s="8"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C51" s="7"/>
-      <c r="E51" s="9"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
@@ -1994,66 +2054,44 @@
       <c r="F52" s="8"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="8"/>
+      <c r="C53" s="7"/>
       <c r="E53" s="9"/>
       <c r="F53" s="8"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C54" s="7"/>
-      <c r="E54" s="8"/>
+      <c r="E54" s="9"/>
       <c r="F54" s="8"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C55" s="7"/>
-      <c r="E55" s="8"/>
+      <c r="E55" s="9"/>
       <c r="F55" s="8"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="11"/>
+      <c r="C56" s="7"/>
       <c r="E56" s="9"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
+      <c r="F56" s="8"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="11"/>
+      <c r="C57" s="7"/>
       <c r="E57" s="9"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="K57" s="4"/>
+      <c r="F57" s="8"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="11"/>
+      <c r="C58" s="8"/>
       <c r="E58" s="9"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="K58" s="4"/>
+      <c r="F58" s="8"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
+      <c r="C59" s="7"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
+      <c r="C60" s="7"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="9"/>
@@ -2072,6 +2110,7 @@
       <c r="F62" s="12"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
+      <c r="K62" s="4"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="9"/>
@@ -2081,23 +2120,24 @@
       <c r="F63" s="12"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
+      <c r="K63" s="4"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="20"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="9"/>
       <c r="H64" s="9"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="20"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="9"/>
       <c r="H65" s="9"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
@@ -2128,21 +2168,21 @@
       <c r="H68" s="9"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="9"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="20"/>
       <c r="H69" s="9"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="9"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="20"/>
       <c r="H70" s="9"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
@@ -2164,29 +2204,49 @@
       <c r="H72" s="9"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="8"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="8"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="8"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="8"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="8"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D78" s="7"/>
@@ -2308,15 +2368,40 @@
       <c r="E101" s="7"/>
       <c r="F101" s="8"/>
     </row>
+    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="8"/>
+    </row>
+    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="8"/>
+    </row>
+    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="8"/>
+    </row>
+    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="8"/>
+    </row>
+    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="8"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -3554,7 +3639,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -3610,7 +3695,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -3618,7 +3703,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>88</v>
@@ -3642,7 +3727,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -3738,7 +3823,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>207</v>
@@ -3778,7 +3863,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>215</v>
@@ -3786,7 +3871,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>221</v>
@@ -3802,7 +3887,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>223</v>
@@ -3810,7 +3895,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>224</v>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75D6C3F-D104-462E-BB6C-8A1068D10C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C45879-7083-4A91-A0C1-E9A6D16C9E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="232">
   <si>
     <t>type</t>
   </si>
@@ -727,6 +727,9 @@
   </si>
   <si>
     <t>data('febre')== 1 | data('temperatura')&gt;38</t>
+  </si>
+  <si>
+    <t>hospital</t>
   </si>
 </sst>
 </file>
@@ -3606,10 +3609,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="24.625" customWidth="1"/>
     <col min="2" max="2" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3817,10 +3820,6 @@
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-    </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>226</v>
@@ -3907,6 +3906,14 @@
       </c>
       <c r="B41" s="2" t="s">
         <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C45879-7083-4A91-A0C1-E9A6D16C9E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B403852-9ABD-4681-9BD8-9FA8B07A6834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="234">
   <si>
     <t>type</t>
   </si>
@@ -681,9 +681,6 @@
     <t>sub_dx2</t>
   </si>
   <si>
-    <t>saida</t>
-  </si>
-  <si>
     <t>child_adult</t>
   </si>
   <si>
@@ -726,10 +723,19 @@
     <t>Febre</t>
   </si>
   <si>
-    <t>data('febre')== 1 | data('temperatura')&gt;38</t>
-  </si>
-  <si>
     <t>hospital</t>
+  </si>
+  <si>
+    <t>data('envio_tdr')==2</t>
+  </si>
+  <si>
+    <t>Motivo de não enviar o paciente a fazer TDR</t>
+  </si>
+  <si>
+    <t>m_envio</t>
+  </si>
+  <si>
+    <t>data('febre')== 1 || data('temperatura')&gt;=37</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1404,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y106"/>
+  <dimension ref="A1:Y105"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1563,7 +1569,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>171</v>
@@ -1798,7 +1804,7 @@
     </row>
     <row r="22" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>24</v>
@@ -1904,9 +1910,9 @@
       <c r="Q29"/>
       <c r="R29"/>
     </row>
-    <row r="30" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>46</v>
@@ -1915,10 +1921,11 @@
         <v>91</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J30" s="5"/>
-      <c r="K30" s="2" t="b">
+      <c r="K30" s="2"/>
+      <c r="L30" s="2" t="b">
         <v>1</v>
       </c>
       <c r="O30" s="2"/>
@@ -1932,10 +1939,10 @@
         <v>92</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K31" s="2"/>
       <c r="O31" s="2"/>
@@ -1954,7 +1961,7 @@
         <v>187</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D33" s="2"/>
       <c r="F33" s="2"/>
@@ -1965,7 +1972,7 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D34" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>46</v>
@@ -1993,6 +2000,12 @@
       <c r="R35"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="D36" s="2"/>
       <c r="F36" s="2"/>
       <c r="O36" s="2"/>
@@ -2003,52 +2016,76 @@
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="C37" s="7"/>
+      <c r="D37" s="8" t="s">
+        <v>4</v>
+      </c>
       <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="F37" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="D39" s="8" t="s">
+      <c r="B39" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="D40" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F40" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C41" s="7"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="8"/>
+      <c r="D41" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D42" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C43" s="7"/>
-      <c r="D43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="H43"/>
-      <c r="I43"/>
+      <c r="B42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="H42"/>
+      <c r="I42"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C49" s="8"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="8"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="8"/>
-      <c r="E50" s="9"/>
+      <c r="C50" s="7"/>
+      <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C51" s="7"/>
-      <c r="E51" s="8"/>
+      <c r="E51" s="9"/>
       <c r="F51" s="8"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
@@ -2077,13 +2114,13 @@
       <c r="F56" s="8"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="7"/>
+      <c r="C57" s="8"/>
       <c r="E57" s="9"/>
       <c r="F57" s="8"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C58" s="8"/>
-      <c r="E58" s="9"/>
+      <c r="C58" s="7"/>
+      <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
@@ -2092,9 +2129,13 @@
       <c r="F59" s="8"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C60" s="7"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="9"/>
@@ -2104,6 +2145,7 @@
       <c r="F61" s="12"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
+      <c r="K61" s="4"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="9"/>
@@ -2123,7 +2165,6 @@
       <c r="F63" s="12"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
-      <c r="K63" s="4"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="9"/>
@@ -2162,12 +2203,12 @@
       <c r="H67" s="9"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="9"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="20"/>
       <c r="H68" s="9"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
@@ -2180,12 +2221,12 @@
       <c r="H69" s="9"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="20"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="9"/>
       <c r="H70" s="9"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
@@ -2243,13 +2284,9 @@
       <c r="H76" s="9"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="8"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D78" s="7"/>
@@ -2391,20 +2428,15 @@
       <c r="E105" s="7"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -3574,7 +3606,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -3587,18 +3619,18 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" t="s">
         <v>218</v>
-      </c>
-      <c r="B7" t="s">
-        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3609,7 +3641,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.625" customWidth="1"/>
@@ -3642,7 +3674,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -3698,7 +3730,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -3706,7 +3738,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>88</v>
@@ -3730,7 +3762,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -3822,7 +3854,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>207</v>
@@ -3860,17 +3892,17 @@
         <v>214</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>215</v>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>221</v>
@@ -3878,7 +3910,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>222</v>
@@ -3886,7 +3918,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>223</v>
@@ -3894,26 +3926,26 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>226</v>
+        <v>10</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>231</v>
+      <c r="B42" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B403852-9ABD-4681-9BD8-9FA8B07A6834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847EF851-4919-4292-82FC-A922634ABE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2051,6 +2051,9 @@
       <c r="G40" s="2" t="s">
         <v>211</v>
       </c>
+      <c r="L40" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D41" s="8" t="s">

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847EF851-4919-4292-82FC-A922634ABE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA3CEA1-8B64-4FF0-BF09-BE856CEB94DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="244">
   <si>
     <t>type</t>
   </si>
@@ -690,9 +690,6 @@
     <t>letra_codigo</t>
   </si>
   <si>
-    <t>data('cs') + calculates.child_adult()</t>
-  </si>
-  <si>
     <t>data('DOB_idade')=='1' ? adate.ageInMonths(data('dn')) : 12 * parseInt(data('ano'),10)</t>
   </si>
   <si>
@@ -736,6 +733,39 @@
   </si>
   <si>
     <t>data('febre')== 1 || data('temperatura')&gt;=37</t>
+  </si>
+  <si>
+    <t>gabu</t>
+  </si>
+  <si>
+    <t>calculates.gabu()== 1 ? data('cs') : (data('cs') + calculates.child_adult())</t>
+  </si>
+  <si>
+    <t>(data('cs') == 'SGC' &amp;&amp; calculates.idade_mes()&gt;=216) ? 1: 0</t>
+  </si>
+  <si>
+    <t>erro_cmi</t>
+  </si>
+  <si>
+    <t>(data('cs') == 'SGA' &amp;&amp; calculates.idade_mes()&lt;216) ? 1: 0</t>
+  </si>
+  <si>
+    <t>erro_hosp</t>
+  </si>
+  <si>
+    <t>O adulto não deve ser introduzido porque Tem ou mais  de 18 anos e estás no Gabú CMI</t>
+  </si>
+  <si>
+    <t>A adulto não deve ser introduzido porque Tem menos de 18 anos y estás no Gabú Hospital</t>
+  </si>
+  <si>
+    <t>calculates.erro_cmi() == 1</t>
+  </si>
+  <si>
+    <t>calculates.erro_hosp() == 1</t>
+  </si>
+  <si>
+    <t>(data('cs')=='SGC' || data('cs')=='SGA')? 1 : 0</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1434,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y105"/>
+  <dimension ref="A1:Y112"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1569,7 +1599,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>171</v>
@@ -1732,98 +1762,96 @@
       <c r="R16"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="19"/>
       <c r="F17" s="2"/>
-      <c r="N17"/>
+      <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17"/>
       <c r="R17"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="F18" s="2"/>
+    <row r="18" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="D18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18"/>
       <c r="R18"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L19" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="B19" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="F19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19"/>
       <c r="R19"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="L20" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="B20" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="F20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20"/>
       <c r="R20"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>201</v>
+        <v>240</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21"/>
       <c r="R21"/>
     </row>
-    <row r="22" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" s="2"/>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="2"/>
+      <c r="N22"/>
       <c r="P22" s="2"/>
       <c r="Q22"/>
       <c r="R22"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="F23" s="2"/>
       <c r="O23" s="2"/>
@@ -1833,16 +1861,16 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -1853,24 +1881,33 @@
       <c r="D25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E25"/>
-      <c r="F25" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" t="s">
-        <v>206</v>
-      </c>
-      <c r="L25" s="2" t="b">
-        <v>1</v>
+      <c r="F25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25"/>
       <c r="R25"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D26" s="2"/>
-      <c r="F26" s="2"/>
+    <row r="26" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="L26" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26"/>
@@ -1885,11 +1922,18 @@
       <c r="R27"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
       <c r="Q28"/>
@@ -1897,58 +1941,43 @@
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" t="s">
-        <v>203</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E29"/>
+      <c r="F29" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" t="s">
+        <v>206</v>
+      </c>
+      <c r="L29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29"/>
       <c r="R29"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D30" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="D30" s="2"/>
+      <c r="F30" s="2"/>
       <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
       <c r="Q30"/>
-    </row>
-    <row r="31" spans="2:18" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="D31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="K31" s="2"/>
+      <c r="R30"/>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D31" s="2"/>
+      <c r="F31" s="2"/>
       <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
       <c r="Q31"/>
+      <c r="R31"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="F32" s="2"/>
       <c r="O32" s="2"/>
@@ -1956,42 +1985,45 @@
       <c r="Q32"/>
       <c r="R32"/>
     </row>
-    <row r="33" spans="1:18" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="F33" s="2"/>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D33" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J33" s="5"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
       <c r="Q33"/>
-      <c r="R33"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:18" ht="47.25" x14ac:dyDescent="0.25">
       <c r="D34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>208</v>
-      </c>
+      <c r="K34" s="2"/>
       <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
       <c r="Q34"/>
-      <c r="R34"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="D35" s="2"/>
       <c r="F35" s="2"/>
       <c r="O35" s="2"/>
@@ -1999,12 +2031,12 @@
       <c r="Q35"/>
       <c r="R35"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D36" s="2"/>
       <c r="F36" s="2"/>
@@ -2014,189 +2046,200 @@
       <c r="R36"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8" t="s">
-        <v>232</v>
+      <c r="D37" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>230</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37"/>
+      <c r="R37"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>198</v>
       </c>
+      <c r="D38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38"/>
+      <c r="R38"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>49</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39"/>
+      <c r="R39"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="19"/>
+      <c r="F45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" t="s">
+        <v>203</v>
+      </c>
+      <c r="P45" s="2"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+      <c r="D47" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F47" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="L40" s="2" t="b">
+      <c r="L47" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D41" s="8" t="s">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D48" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F48" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="H42"/>
-      <c r="I42"/>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="8"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="7"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C51" s="7"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="7"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="8"/>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="7"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="8"/>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C54" s="7"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="8"/>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C55" s="7"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="8"/>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C56" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="H49"/>
+      <c r="I49"/>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C56" s="8"/>
       <c r="E56" s="9"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="8"/>
-      <c r="E57" s="9"/>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C57" s="7"/>
+      <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C58" s="7"/>
-      <c r="E58" s="8"/>
+      <c r="E58" s="9"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C59" s="7"/>
-      <c r="E59" s="8"/>
+      <c r="E59" s="9"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="11"/>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C60" s="7"/>
       <c r="E60" s="9"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="11"/>
+      <c r="F60" s="8"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C61" s="7"/>
       <c r="E61" s="9"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="K61" s="4"/>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="11"/>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C62" s="7"/>
       <c r="E62" s="9"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="K62" s="4"/>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="11"/>
+      <c r="F62" s="8"/>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C63" s="7"/>
       <c r="E63" s="9"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="11"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C64" s="8"/>
       <c r="E64" s="9"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F64" s="8"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C65" s="7"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C66" s="7"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
       <c r="D67" s="11"/>
@@ -2205,25 +2248,27 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="20"/>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="9"/>
       <c r="H68" s="9"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="20"/>
+      <c r="K68" s="4"/>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="9"/>
       <c r="H69" s="9"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
       <c r="D70" s="11"/>
@@ -2232,7 +2277,7 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
       <c r="D71" s="11"/>
@@ -2241,7 +2286,7 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
       <c r="D72" s="11"/>
@@ -2250,7 +2295,7 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
       <c r="D73" s="11"/>
@@ -2259,7 +2304,7 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="11"/>
@@ -2268,120 +2313,148 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="9"/>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="20"/>
       <c r="H75" s="9"/>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="9"/>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="20"/>
       <c r="H76" s="9"/>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="8"/>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="8"/>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="8"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="8"/>
-    </row>
-    <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="8"/>
-    </row>
-    <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="8"/>
-    </row>
-    <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="8"/>
-    </row>
-    <row r="84" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="8"/>
@@ -2431,15 +2504,50 @@
       <c r="E105" s="7"/>
       <c r="F105" s="8"/>
     </row>
+    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="8"/>
+    </row>
+    <row r="107" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="8"/>
+    </row>
+    <row r="108" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="8"/>
+    </row>
+    <row r="109" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="8"/>
+    </row>
+    <row r="110" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="8"/>
+    </row>
+    <row r="111" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="8"/>
+    </row>
+    <row r="112" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="8"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="F75:F76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -3573,7 +3681,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CAEF6-746F-4DFF-99B1-6DB036574858}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -3609,7 +3717,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -3621,19 +3729,43 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>216</v>
+      <c r="A6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>217</v>
       </c>
-      <c r="B7" t="s">
-        <v>218</v>
+      <c r="B10" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3677,7 +3809,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -3733,7 +3865,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -3741,7 +3873,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>88</v>
@@ -3765,7 +3897,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -3857,7 +3989,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>207</v>
@@ -3897,10 +4029,10 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -3908,23 +4040,23 @@
         <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -3932,15 +4064,15 @@
         <v>10</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -3948,7 +4080,7 @@
         <v>4</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA3CEA1-8B64-4FF0-BF09-BE856CEB94DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B572211-F169-476D-A2B8-63E3A405248D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -1397,7 +1397,7 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2022022800</v>
+        <v>2020030801</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B572211-F169-476D-A2B8-63E3A405248D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86640AF6-0891-4902-9B5E-2F8BFFEE2AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="240">
   <si>
     <t>type</t>
   </si>
@@ -660,9 +660,6 @@
     <t>envio_tdr</t>
   </si>
   <si>
-    <t>O/A paciente foi enviada a fazer TDR</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -723,16 +720,7 @@
     <t>hospital</t>
   </si>
   <si>
-    <t>data('envio_tdr')==2</t>
-  </si>
-  <si>
-    <t>Motivo de não enviar o paciente a fazer TDR</t>
-  </si>
-  <si>
     <t>m_envio</t>
-  </si>
-  <si>
-    <t>data('febre')== 1 || data('temperatura')&gt;=37</t>
   </si>
   <si>
     <t>gabu</t>
@@ -1397,7 +1385,7 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2020030801</v>
+        <v>2020040701</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
@@ -1418,7 +1406,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -1434,7 +1422,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y112"/>
+  <dimension ref="A1:Y105"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1599,7 +1587,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>171</v>
@@ -1766,7 +1754,7 @@
         <v>187</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D17" s="2"/>
       <c r="F17" s="2"/>
@@ -1780,13 +1768,13 @@
         <v>60</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1809,7 +1797,7 @@
         <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D20" s="2"/>
       <c r="F20" s="2"/>
@@ -1823,13 +1811,13 @@
         <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1894,7 +1882,7 @@
     </row>
     <row r="26" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>24</v>
@@ -1987,7 +1975,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D33" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>46</v>
@@ -1996,7 +1984,7 @@
         <v>91</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="2"/>
@@ -2014,10 +2002,10 @@
         <v>92</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K34" s="2"/>
       <c r="O34" s="2"/>
@@ -2031,32 +2019,18 @@
       <c r="Q35"/>
       <c r="R35"/>
     </row>
-    <row r="36" spans="1:18" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36"/>
-      <c r="R36"/>
-    </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D37" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
+      </c>
+      <c r="L37" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -2064,182 +2038,182 @@
       <c r="R37"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="D38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" s="19"/>
+      <c r="F38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" t="s">
+        <v>203</v>
+      </c>
       <c r="P38" s="2"/>
       <c r="Q38"/>
       <c r="R38"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
-      <c r="Q39"/>
-      <c r="R39"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40"/>
-      <c r="C40" s="7"/>
       <c r="D40" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="L40" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D41" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L44" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
-      <c r="Q44"/>
-      <c r="R44"/>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D45" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="19"/>
-      <c r="F45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N45" t="s">
-        <v>203</v>
-      </c>
-      <c r="P45" s="2"/>
-      <c r="Q45"/>
-      <c r="R45"/>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="D47" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="L47" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D48" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="7" t="s">
+      <c r="F41" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G41" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="H49"/>
-      <c r="I49"/>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C56" s="8"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="H42"/>
+      <c r="I42"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C49" s="8"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="8"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C50" s="7"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C51" s="7"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="8"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C52" s="7"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="8"/>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C53" s="7"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="8"/>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C54" s="7"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="8"/>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C55" s="7"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="8"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C56" s="7"/>
       <c r="E56" s="9"/>
       <c r="F56" s="8"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C57" s="7"/>
-      <c r="E57" s="8"/>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C57" s="8"/>
+      <c r="E57" s="9"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C58" s="7"/>
-      <c r="E58" s="9"/>
+      <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C59" s="7"/>
-      <c r="E59" s="9"/>
+      <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C60" s="7"/>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="11"/>
       <c r="E60" s="9"/>
-      <c r="F60" s="8"/>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C61" s="7"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="11"/>
       <c r="E61" s="9"/>
-      <c r="F61" s="8"/>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C62" s="7"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="11"/>
       <c r="E62" s="9"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C63" s="7"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="K62" s="4"/>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="11"/>
       <c r="E63" s="9"/>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C64" s="8"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="11"/>
       <c r="E64" s="9"/>
-      <c r="F64" s="8"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C65" s="7"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C66" s="7"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F64" s="12"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
       <c r="D67" s="11"/>
@@ -2248,27 +2222,25 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="9"/>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="20"/>
       <c r="H68" s="9"/>
-      <c r="K68" s="4"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="9"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="20"/>
       <c r="H69" s="9"/>
-      <c r="K69" s="4"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
       <c r="D70" s="11"/>
@@ -2277,7 +2249,7 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
       <c r="D71" s="11"/>
@@ -2286,7 +2258,7 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
       <c r="D72" s="11"/>
@@ -2295,7 +2267,7 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
       <c r="D73" s="11"/>
@@ -2304,7 +2276,7 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="11"/>
@@ -2313,148 +2285,120 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="20"/>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="9"/>
       <c r="H75" s="9"/>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="20"/>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="9"/>
       <c r="H76" s="9"/>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-    </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-    </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="8"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="8"/>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="8"/>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="8"/>
+    </row>
+    <row r="81" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="8"/>
+    </row>
+    <row r="82" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="8"/>
+    </row>
+    <row r="83" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="8"/>
+    </row>
+    <row r="84" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="8"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="8"/>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="8"/>
@@ -2504,50 +2448,15 @@
       <c r="E105" s="7"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="8"/>
-    </row>
-    <row r="107" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="8"/>
-    </row>
-    <row r="108" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="8"/>
-    </row>
-    <row r="109" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="8"/>
-    </row>
-    <row r="110" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="8"/>
-    </row>
-    <row r="111" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="8"/>
-    </row>
-    <row r="112" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:F69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -3717,7 +3626,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -3730,42 +3639,42 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3809,7 +3718,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -3865,7 +3774,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -3873,7 +3782,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>88</v>
@@ -3897,7 +3806,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -3989,7 +3898,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>207</v>
@@ -4000,7 +3909,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4008,7 +3917,7 @@
         <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -4016,7 +3925,7 @@
         <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4024,15 +3933,15 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4040,23 +3949,23 @@
         <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -4064,15 +3973,15 @@
         <v>10</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -4080,7 +3989,7 @@
         <v>4</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86640AF6-0891-4902-9B5E-2F8BFFEE2AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A553FB-AFE3-4F93-8B63-1EDE2CC9EADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="238">
   <si>
     <t>type</t>
   </si>
@@ -633,9 +633,6 @@
     <t>end if</t>
   </si>
   <si>
-    <t>Introduza o numero se serie do cartao: {{calculates.letra_codigo}}</t>
-  </si>
-  <si>
     <t>Nome e Apelido</t>
   </si>
   <si>
@@ -643,9 +640,6 @@
   </si>
   <si>
     <t>Sexo</t>
-  </si>
-  <si>
-    <t>calculates.letra_codigo() + data('numero_codigo')</t>
   </si>
   <si>
     <t>Peso</t>
@@ -1406,7 +1400,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1422,7 +1416,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y105"/>
+  <dimension ref="A1:Y99"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
@@ -1587,7 +1581,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>171</v>
@@ -1754,7 +1748,7 @@
         <v>187</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D17" s="2"/>
       <c r="F17" s="2"/>
@@ -1768,13 +1762,13 @@
         <v>60</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1797,7 +1791,7 @@
         <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D20" s="2"/>
       <c r="F20" s="2"/>
@@ -1811,13 +1805,13 @@
         <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1855,7 +1849,7 @@
         <v>23</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L24" s="2" t="b">
         <v>1</v>
@@ -1873,7 +1867,7 @@
         <v>58</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -1882,7 +1876,7 @@
     </row>
     <row r="26" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>24</v>
@@ -1891,7 +1885,7 @@
         <v>24</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L26" s="2" t="b">
         <v>1</v>
@@ -1917,10 +1911,10 @@
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -1936,7 +1930,7 @@
         <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>1</v>
@@ -1947,6 +1941,9 @@
       <c r="R29"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="F30" s="2"/>
       <c r="O30" s="2"/>
@@ -1955,198 +1952,194 @@
       <c r="R30"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J31" s="5"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
       <c r="Q31"/>
-      <c r="R31"/>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+    </row>
+    <row r="32" spans="2:18" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="D32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="Q32"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="D34" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="L34" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D35" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32"/>
-      <c r="R32"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D33" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J33" s="5"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2"/>
-      <c r="Q33"/>
-    </row>
-    <row r="34" spans="1:18" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="D34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="Q34"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
-      <c r="Q37"/>
-      <c r="R37"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D38" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N38" t="s">
-        <v>203</v>
-      </c>
-      <c r="P38" s="2"/>
-      <c r="Q38"/>
-      <c r="R38"/>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="D40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L40" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D41" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="H42"/>
-      <c r="I42"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="H36"/>
+      <c r="I36"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="8"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="7"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C45" s="7"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="8"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C46" s="7"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="8"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C47" s="7"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="8"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C48" s="7"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="8"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="8"/>
+      <c r="C49" s="7"/>
       <c r="E49" s="9"/>
       <c r="F49" s="8"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C50" s="7"/>
-      <c r="E50" s="8"/>
+      <c r="E50" s="9"/>
       <c r="F50" s="8"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C51" s="7"/>
+      <c r="C51" s="8"/>
       <c r="E51" s="9"/>
       <c r="F51" s="8"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C52" s="7"/>
-      <c r="E52" s="9"/>
+      <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C53" s="7"/>
-      <c r="E53" s="9"/>
+      <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C54" s="7"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="11"/>
       <c r="E54" s="9"/>
-      <c r="F54" s="8"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C55" s="7"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="11"/>
       <c r="E55" s="9"/>
-      <c r="F55" s="8"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="K55" s="4"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C56" s="7"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="11"/>
       <c r="E56" s="9"/>
-      <c r="F56" s="8"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="K56" s="4"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="11"/>
       <c r="E57" s="9"/>
-      <c r="F57" s="8"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C58" s="7"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C59" s="7"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="9"/>
@@ -2165,25 +2158,23 @@
       <c r="F61" s="12"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
-      <c r="K61" s="4"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="9"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="20"/>
       <c r="H62" s="9"/>
-      <c r="K62" s="4"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="9"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="20"/>
       <c r="H63" s="9"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
@@ -2223,21 +2214,21 @@
       <c r="H67" s="9"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="20"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="9"/>
       <c r="H68" s="9"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="20"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="9"/>
       <c r="H69" s="9"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
@@ -2250,58 +2241,34 @@
       <c r="H70" s="9"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="8"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="8"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="8"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="8"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="8"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="8"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D77" s="7"/>
@@ -2418,45 +2385,15 @@
       <c r="E99" s="7"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="8"/>
-    </row>
-    <row r="101" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="8"/>
-    </row>
-    <row r="102" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="8"/>
-    </row>
-    <row r="103" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="8"/>
-    </row>
-    <row r="104" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="8"/>
-    </row>
-    <row r="105" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="8"/>
-    </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -3626,7 +3563,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -3639,42 +3576,42 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -3718,7 +3655,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -3774,7 +3711,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -3782,7 +3719,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>88</v>
@@ -3806,7 +3743,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -3898,10 +3835,10 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3909,7 +3846,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3917,7 +3854,7 @@
         <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3925,7 +3862,7 @@
         <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3933,15 +3870,15 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -3949,23 +3886,23 @@
         <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -3973,15 +3910,15 @@
         <v>10</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -3989,7 +3926,7 @@
         <v>4</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
+++ b/app/config/tables/sentinela/forms/sentinela/sentinela.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\code\odkx\sentinela\app\config\tables\sentinela\forms\sentinela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A553FB-AFE3-4F93-8B63-1EDE2CC9EADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16885435-3E0F-49D8-82C5-D4E6101B0316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="246">
   <si>
     <t>type</t>
   </si>
@@ -591,9 +591,6 @@
     <t>nota_1</t>
   </si>
   <si>
-    <t>Centro: {{data.csname}} Data: {{calculates.hoje_display}}</t>
-  </si>
-  <si>
     <t>Idade ou data de nascimento?</t>
   </si>
   <si>
@@ -748,6 +745,33 @@
   </si>
   <si>
     <t>(data('cs')=='SGC' || data('cs')=='SGA')? 1 : 0</t>
+  </si>
+  <si>
+    <t>erro_consultorio</t>
+  </si>
+  <si>
+    <t>calculates.idade_mes()&gt;=216 &amp;&amp; data('consultorio')=="CRIANCA"</t>
+  </si>
+  <si>
+    <t>erro_consultorio_a</t>
+  </si>
+  <si>
+    <t>erro_consultorio_c</t>
+  </si>
+  <si>
+    <t>A adulto não deve ser introduzido porque Tem menos de 18 anos y estás no Consultorio de criança</t>
+  </si>
+  <si>
+    <t>A Criança não deve ser introduzido porque Tem menos de 18 anos y estás no Consultorio de adulto</t>
+  </si>
+  <si>
+    <t>Centro: {{data.csname}} Data: {{calculates.hoje_display}}  Consulta de: {{data.consultor}}</t>
+  </si>
+  <si>
+    <t>calculates.idade_mes()&lt;216 &amp;&amp; data('consultor')=="ADULTO"</t>
+  </si>
+  <si>
+    <t>calculates.idade_mes()&gt;=216 &amp;&amp; data('consultor')=="CRIANCA"</t>
   </si>
 </sst>
 </file>
@@ -873,7 +897,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -890,26 +914,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -918,12 +927,6 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1379,7 +1382,7 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2020040701</v>
+        <v>2024050200</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
@@ -1400,7 +1403,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -1416,15 +1419,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y99"/>
+  <dimension ref="A1:Y78"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="15.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.125" style="2" customWidth="1"/>
     <col min="9" max="9" width="29.75" style="2" customWidth="1"/>
@@ -1447,19 +1450,19 @@
       <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I1" t="s">
@@ -1480,10 +1483,10 @@
       <c r="N1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="10" t="s">
         <v>82</v>
       </c>
       <c r="Q1" t="s">
@@ -1515,9 +1518,8 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="8"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1528,8 +1530,6 @@
       <c r="B3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="F3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3"/>
@@ -1542,7 +1542,7 @@
       <c r="F4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="6"/>
       <c r="K4" s="2"/>
       <c r="M4" t="s">
         <v>78</v>
@@ -1560,7 +1560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>60</v>
       </c>
@@ -1568,9 +1568,9 @@
         <v>184</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J5" s="19"/>
+        <v>243</v>
+      </c>
+      <c r="J5" s="6"/>
       <c r="K5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>171</v>
@@ -1590,7 +1590,7 @@
         <v>171</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>1</v>
@@ -1602,13 +1602,11 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="F7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7"/>
@@ -1625,7 +1623,7 @@
         <v>25</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1634,10 +1632,8 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
+        <v>188</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9"/>
@@ -1651,13 +1647,13 @@
         <v>27</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -1666,13 +1662,11 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="F11" s="2"/>
+        <v>192</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11"/>
@@ -1686,16 +1680,16 @@
         <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -1703,8 +1697,6 @@
       <c r="R12"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D13" s="2"/>
-      <c r="F13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13"/>
@@ -1712,10 +1704,8 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="F14" s="2"/>
+        <v>197</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14"/>
@@ -1723,10 +1713,8 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="F15" s="2"/>
+        <v>197</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15"/>
@@ -1736,8 +1724,6 @@
       <c r="B16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="F16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16"/>
@@ -1745,13 +1731,11 @@
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="F17" s="2"/>
+        <v>234</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17"/>
@@ -1762,13 +1746,13 @@
         <v>60</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1777,10 +1761,8 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="F19" s="2"/>
+        <v>197</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19"/>
@@ -1788,13 +1770,11 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="F20" s="2"/>
+        <v>235</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20"/>
@@ -1805,13 +1785,13 @@
         <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1820,39 +1800,38 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="E22" s="6"/>
       <c r="N22"/>
       <c r="P22" s="2"/>
       <c r="Q22"/>
       <c r="R22"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="F23" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23"/>
       <c r="R23"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>23</v>
+        <v>60</v>
+      </c>
+      <c r="F24" t="s">
+        <v>240</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L24" s="2" t="b">
-        <v>1</v>
+        <v>241</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -1860,61 +1839,46 @@
       <c r="R24"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="O25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="N25"/>
       <c r="P25" s="2"/>
       <c r="Q25"/>
       <c r="R25"/>
     </row>
-    <row r="26" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="L26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2"/>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E26" s="6"/>
+      <c r="N26"/>
       <c r="P26" s="2"/>
       <c r="Q26"/>
       <c r="R26"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D27" s="2"/>
-      <c r="F27" s="2"/>
+    <row r="27" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27"/>
       <c r="R27"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>60</v>
+      </c>
+      <c r="F28" t="s">
+        <v>239</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>203</v>
+        <v>242</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -1922,478 +1886,401 @@
       <c r="R28"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29"/>
-      <c r="F29" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" t="s">
-        <v>204</v>
-      </c>
-      <c r="L29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="N29"/>
       <c r="P29" s="2"/>
       <c r="Q29"/>
       <c r="R29"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="E30" s="6"/>
+      <c r="N30"/>
       <c r="P30" s="2"/>
       <c r="Q30"/>
       <c r="R30"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="D31" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2" t="b">
+      <c r="B31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="L32" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="O31" s="2"/>
-      <c r="Q31"/>
-    </row>
-    <row r="32" spans="2:18" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="D32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="K32" s="2"/>
       <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
       <c r="Q32"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-      <c r="D34" s="8" t="s">
+      <c r="R32"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D33" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>207</v>
+      <c r="F33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+    </row>
+    <row r="34" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D34" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="L34" s="2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D35" s="8" t="s">
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37"/>
+      <c r="F37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" t="s">
+        <v>203</v>
+      </c>
+      <c r="L37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D39" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J39" s="5"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="Q39"/>
+    </row>
+    <row r="40" spans="1:18" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="D40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="Q40"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="D42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L42" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D43" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="H36"/>
-      <c r="I36"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="8"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="8"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C44" s="7"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C45" s="7"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C46" s="7"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="8"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C47" s="7"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="8"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C48" s="7"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="7"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="7"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="8"/>
+      <c r="H44"/>
+      <c r="I44"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C51" s="8"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="7"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
+      <c r="E51" s="6"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="7"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
+      <c r="E53" s="6"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
+      <c r="E54" s="6"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="K55" s="4"/>
+      <c r="E55" s="6"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="K56" s="4"/>
+      <c r="E56" s="6"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
+      <c r="E57" s="6"/>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
+      <c r="E58" s="6"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
+      <c r="E59" s="6"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="9"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="9"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="K63" s="4"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="K64" s="4"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="6"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="8"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="6"/>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="8"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="8"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="8"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="8"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="8"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="8"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="8"/>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="8"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="8"/>
-    </row>
-    <row r="81" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="8"/>
-    </row>
-    <row r="82" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="8"/>
-    </row>
-    <row r="83" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="8"/>
-    </row>
-    <row r="84" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="8"/>
-    </row>
-    <row r="85" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="8"/>
-    </row>
-    <row r="86" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="8"/>
-    </row>
-    <row r="87" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="8"/>
-    </row>
-    <row r="88" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="8"/>
-    </row>
-    <row r="89" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="8"/>
-    </row>
-    <row r="90" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="8"/>
-    </row>
-    <row r="91" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="8"/>
-    </row>
-    <row r="92" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="8"/>
-    </row>
-    <row r="93" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="8"/>
-    </row>
-    <row r="94" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="8"/>
-    </row>
-    <row r="95" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="8"/>
-    </row>
-    <row r="96" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="8"/>
-    </row>
-    <row r="97" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="8"/>
-    </row>
-    <row r="98" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="8"/>
-    </row>
-    <row r="99" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="8"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G62:G63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:F71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -2667,7 +2554,7 @@
       <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -2678,7 +2565,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -2689,7 +2576,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -2700,7 +2587,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -2711,7 +2598,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -2722,7 +2609,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -2733,7 +2620,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -2744,7 +2631,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2755,7 +2642,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -2766,7 +2653,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2777,7 +2664,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2788,7 +2675,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2799,7 +2686,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -2810,7 +2697,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2821,7 +2708,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -2832,7 +2719,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -2843,7 +2730,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -2854,7 +2741,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -2865,7 +2752,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -2876,7 +2763,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -2887,7 +2774,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -2898,7 +2785,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -2909,7 +2796,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -2920,7 +2807,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -2931,7 +2818,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -2942,7 +2829,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -2953,7 +2840,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -2964,7 +2851,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -2975,7 +2862,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -2986,7 +2873,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -3390,38 +3277,38 @@
     <col min="11" max="11" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3447,7 +3334,7 @@
       <c r="G2" t="s">
         <v>178</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="12" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3478,17 +3365,17 @@
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="10" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3527,7 +3414,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02CAEF6-746F-4DFF-99B1-6DB036574858}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -3563,7 +3450,7 @@
         <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
@@ -3576,42 +3463,50 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3630,10 +3525,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3655,7 +3550,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>171</v>
@@ -3711,7 +3606,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -3719,7 +3614,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>88</v>
@@ -3743,7 +3638,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>91</v>
@@ -3835,10 +3730,10 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -3846,7 +3741,7 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -3854,7 +3749,7 @@
         <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -3862,7 +3757,7 @@
         <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -3870,15 +3765,15 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -3886,23 +3781,23 @@
         <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -3910,23 +3805,23 @@
         <v>10</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>
